--- a/data/trans_dic/P5B_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P5B_R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con calidad medioambiental mala o muy mala en la zona de residencia</t>
+          <t>Hogares con calidad medioambiental mala o muy mala en la zona de residencia (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,27 +717,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 12,8</t>
+          <t>2,01; 12,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,92</t>
+          <t>0,0; 7,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,26</t>
+          <t>0,0; 10,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,47</t>
+          <t>0,0; 6,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 12,99</t>
+          <t>1,25; 11,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -746,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,77</t>
+          <t>0,0; 7,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 9,09</t>
+          <t>0,88; 9,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 9,78</t>
+          <t>2,67; 9,65</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,43</t>
+          <t>0,51; 4,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,55</t>
+          <t>0,67; 6,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,68</t>
+          <t>0,74; 6,14</t>
         </is>
       </c>
     </row>
@@ -798,7 +799,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -838,7 +839,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 6,17</t>
+          <t>2,46; 6,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,18</t>
+          <t>0,66; 3,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,0</t>
+          <t>1,22; 3,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 26,01</t>
+          <t>0,51; 27,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,65</t>
+          <t>1,89; 4,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,04</t>
+          <t>0,79; 3,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,82</t>
+          <t>0,2; 1,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,35</t>
+          <t>0,11; 1,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,73</t>
+          <t>2,42; 4,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,51</t>
+          <t>0,88; 2,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,31</t>
+          <t>0,9; 2,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 13,22</t>
+          <t>0,45; 13,25</t>
         </is>
       </c>
     </row>
@@ -933,7 +934,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -953,7 +954,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -963,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -973,7 +974,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -983,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,81</t>
+          <t>0,96; 5,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 7,23</t>
+          <t>1,3; 7,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,55</t>
+          <t>0,51; 5,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 3,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,31</t>
+          <t>0,46; 4,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 6,01</t>
+          <t>0,83; 5,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,19</t>
+          <t>1,1; 4,22</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,25</t>
+          <t>1,05; 4,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,57</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,3</t>
+          <t>0,69; 3,3</t>
         </is>
       </c>
     </row>
@@ -1073,47 +1074,47 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>1,78%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,71%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,46</t>
+          <t>2,55; 5,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,13</t>
+          <t>1,13; 3,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,77</t>
+          <t>1,07; 2,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 19,93</t>
+          <t>0,51; 16,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,41</t>
+          <t>1,91; 4,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,59</t>
+          <t>0,84; 2,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,09</t>
+          <t>0,58; 2,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,11</t>
+          <t>0,69; 2,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,31</t>
+          <t>2,64; 4,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,54</t>
+          <t>1,14; 2,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,11</t>
+          <t>0,93; 2,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 9,54</t>
+          <t>0,87; 8,54</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con calidad medioambiental mala o muy mala en la zona de residencia (tasa de respuesta: 99,82%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3360</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1228</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2598</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1264</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2199</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>5957</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2507</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3030</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1137; 7239</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3924</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4350</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3809</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>643; 6007</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4384</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4032</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>546; 6161</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2884; 10403</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>598; 5220</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>619; 5692</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>859; 7165</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>12380</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4779</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8129</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>29841</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>10807</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5569</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2663</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>23187</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>10349</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>10847</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>32504</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>7629; 19053</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1995; 9574</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4232; 13317</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2333; 128745</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>6687; 17147</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2684; 10624</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>765; 6700</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>588; 6726</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>16086; 31645</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>5652; 16556</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>6516; 16818</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>4436; 129511</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3535</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4162</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2514</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1515</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>4880</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>6050</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>5677</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>5490</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1314; 7991</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1508; 8799</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2750</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>636; 6254</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5408</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>644; 5989</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1508; 10557</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2871; 10979</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2636; 11276</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 6331</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2282; 10919</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>19275</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9636</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9356</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31282</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>15919</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8349</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6299</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>9741</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>35195</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>17986</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>15655</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>41023</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>12821; 26356</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>5359; 15093</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5589; 15446</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>3383; 111418</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>10112; 22704</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4495; 14371</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3294; 11606</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>5221; 17062</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>27284; 46386</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>11532; 26127</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>10137; 22690</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>12445; 121689</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P5B_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P5B_R-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 12,82</t>
+          <t>2,19; 13,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,07</t>
+          <t>0,0; 6,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,7</t>
+          <t>0,0; 9,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,97</t>
+          <t>0,0; 8,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 11,69</t>
+          <t>1,31; 12,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,06</t>
+          <t>0,0; 7,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,87</t>
+          <t>0,0; 9,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 9,94</t>
+          <t>0,86; 9,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 9,65</t>
+          <t>2,62; 9,99</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,44</t>
+          <t>0,52; 4,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,19</t>
+          <t>0,7; 6,55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,14</t>
+          <t>0,75; 6,48</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,14</t>
+          <t>2,56; 6,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,15</t>
+          <t>0,69; 3,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,85</t>
+          <t>1,33; 3,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 27,96</t>
+          <t>0,52; 24,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,85</t>
+          <t>1,83; 4,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,13</t>
+          <t>0,78; 3,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,77</t>
+          <t>0,18; 1,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,3</t>
+          <t>0,21; 1,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,77</t>
+          <t>2,47; 4,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,57</t>
+          <t>0,96; 2,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,32</t>
+          <t>0,88; 2,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 13,25</t>
+          <t>0,5; 18,28</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,85</t>
+          <t>0,91; 5,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,58</t>
+          <t>1,25; 7,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 2,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,06</t>
+          <t>0,5; 5,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,99</t>
+          <t>0,0; 3,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,28</t>
+          <t>0,46; 4,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 5,81</t>
+          <t>1,03; 5,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,22</t>
+          <t>1,04; 4,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,48</t>
+          <t>1,05; 4,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,23; 2,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,3</t>
+          <t>0,72; 3,35</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,24</t>
+          <t>2,7; 5,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,17</t>
+          <t>1,09; 3,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,95</t>
+          <t>1,04; 2,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 16,78</t>
+          <t>0,51; 18,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,3</t>
+          <t>2,0; 4,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,67</t>
+          <t>0,86; 2,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,03</t>
+          <t>0,55; 2,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,24</t>
+          <t>0,74; 2,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,64; 4,5</t>
+          <t>2,58; 4,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,58</t>
+          <t>1,19; 2,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,08</t>
+          <t>0,91; 2,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,54</t>
+          <t>0,91; 11,02</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1137; 7239</t>
+          <t>1237; 7396</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3924</t>
+          <t>0; 3463</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4350</t>
+          <t>0; 4061</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3809</t>
+          <t>0; 4447</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>643; 6007</t>
+          <t>672; 6434</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4384</t>
+          <t>0; 4458</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4032</t>
+          <t>0; 4744</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>546; 6161</t>
+          <t>533; 6062</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2884; 10403</t>
+          <t>2820; 10769</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>598; 5220</t>
+          <t>607; 5650</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>619; 5692</t>
+          <t>647; 6021</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>859; 7165</t>
+          <t>870; 7566</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7629; 19053</t>
+          <t>7929; 19338</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1995; 9574</t>
+          <t>2097; 9980</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4232; 13317</t>
+          <t>4594; 13612</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2333; 128745</t>
+          <t>2377; 112153</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6687; 17147</t>
+          <t>6457; 15693</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2684; 10624</t>
+          <t>2660; 10602</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>765; 6700</t>
+          <t>682; 6854</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>588; 6726</t>
+          <t>1088; 6986</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16086; 31645</t>
+          <t>16427; 31510</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5652; 16556</t>
+          <t>6201; 17083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6516; 16818</t>
+          <t>6388; 16646</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4436; 129511</t>
+          <t>4887; 178585</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1314; 7991</t>
+          <t>1238; 7686</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1508; 8799</t>
+          <t>1455; 8171</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1935,47 +1935,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2750</t>
+          <t>0; 3333</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>636; 6254</t>
+          <t>621; 6312</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5408</t>
+          <t>0; 5392</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>644; 5989</t>
+          <t>649; 6201</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1508; 10557</t>
+          <t>1871; 10289</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2871; 10979</t>
+          <t>2694; 10956</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2636; 11276</t>
+          <t>2640; 10444</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 6331</t>
+          <t>646; 6616</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2282; 10919</t>
+          <t>2388; 11075</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12821; 26356</t>
+          <t>13613; 28203</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5359; 15093</t>
+          <t>5181; 16126</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5589; 15446</t>
+          <t>5434; 15144</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3383; 111418</t>
+          <t>3409; 121848</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10112; 22704</t>
+          <t>10573; 23863</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4495; 14371</t>
+          <t>4595; 14072</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3294; 11606</t>
+          <t>3152; 11816</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5221; 17062</t>
+          <t>5599; 16017</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27284; 46386</t>
+          <t>26612; 44725</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11532; 26127</t>
+          <t>12034; 26919</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10137; 22690</t>
+          <t>9970; 22026</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12445; 121689</t>
+          <t>12891; 157028</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P5B_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P5B_R-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,06%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5,95%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,25%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3,02%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 13,1</t>
+          <t>1,29; 12,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,24</t>
+          <t>0,0; 7,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,99</t>
+          <t>0,0; 8,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,13</t>
+          <t>0,8; 9,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 12,52</t>
+          <t>2,2; 12,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,18</t>
+          <t>0,0; 6,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,26</t>
+          <t>0,0; 10,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 9,78</t>
+          <t>0,0; 11,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,62; 9,99</t>
+          <t>2,89; 9,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,81</t>
+          <t>0,51; 4,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,55</t>
+          <t>0,72; 6,55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,48</t>
+          <t>0,63; 7,62</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>3,99%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,57%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,35%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,48%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 6,23</t>
+          <t>1,8; 4,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,28</t>
+          <t>0,78; 3,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,93</t>
+          <t>0,16; 1,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 24,35</t>
+          <t>0,11; 1,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,44</t>
+          <t>2,32; 6,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,12</t>
+          <t>0,71; 3,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,81</t>
+          <t>1,24; 3,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,35</t>
+          <t>0,47; 4,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,75</t>
+          <t>2,46; 4,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,65</t>
+          <t>0,88; 2,54</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,29</t>
+          <t>0,92; 2,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 18,28</t>
+          <t>0,43; 2,14</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2,59%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,59%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,63</t>
+          <t>0,52; 5,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,04</t>
+          <t>0,0; 3,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0,46; 4,31</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1,14; 6,28</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,97; 5,81</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,34; 7,57</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,24</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,5; 5,11</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,98</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,46; 4,43</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,66</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,21</t>
+          <t>1,05; 4,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,15</t>
+          <t>0,96; 4,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,4</t>
+          <t>0,24; 2,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,35</t>
+          <t>0,73; 3,45</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3,83%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,03%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,79%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,71%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,6</t>
+          <t>1,86; 4,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,39</t>
+          <t>0,88; 2,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,9</t>
+          <t>0,55; 2,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 18,35</t>
+          <t>0,71; 2,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,51</t>
+          <t>2,59; 5,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,62</t>
+          <t>1,18; 3,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,07</t>
+          <t>1,02; 2,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,11</t>
+          <t>0,5; 2,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,33</t>
+          <t>2,53; 4,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,66</t>
+          <t>1,21; 2,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,01</t>
+          <t>0,91; 2,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 11,02</t>
+          <t>0,77; 2,14</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2598</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1264</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>3360</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>695</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1228</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2598</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1264</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>870</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2892</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1237; 7396</t>
+          <t>665; 6674</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3463</t>
+          <t>0; 4382</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4061</t>
+          <t>0; 4491</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4447</t>
+          <t>457; 5255</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>672; 6434</t>
+          <t>1240; 7229</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4458</t>
+          <t>0; 3842</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4744</t>
+          <t>0; 4170</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>533; 6062</t>
+          <t>0; 5432</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2820; 10769</t>
+          <t>3119; 10543</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>607; 5650</t>
+          <t>603; 5204</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>647; 6021</t>
+          <t>660; 6015</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>870; 7566</t>
+          <t>650; 7885</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10807</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5569</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2369</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>12380</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4779</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>8129</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>29841</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10807</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5569</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32504</t>
+          <t>8122</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7929; 19338</t>
+          <t>6367; 16461</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2097; 9980</t>
+          <t>2644; 10317</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4594; 13612</t>
+          <t>590; 7179</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2377; 112153</t>
+          <t>501; 6523</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6457; 15693</t>
+          <t>7192; 19136</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2660; 10602</t>
+          <t>2152; 9464</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>682; 6854</t>
+          <t>4303; 13052</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1088; 6986</t>
+          <t>2019; 17762</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16427; 31510</t>
+          <t>16351; 31416</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6201; 17083</t>
+          <t>5664; 16360</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6388; 16646</t>
+          <t>6655; 17023</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4887; 178585</t>
+          <t>3913; 19455</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,62 +1852,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2514</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1515</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4871</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>3535</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>4162</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2514</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1515</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>6050</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>5677</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>2301</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>4880</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>6050</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>5677</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5490</t>
+          <t>5491</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1238; 7686</t>
+          <t>643; 6853</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1455; 8171</t>
+          <t>0; 4938</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>646; 6029</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1903; 10477</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1332; 7939</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1552; 8793</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3333</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>621; 6312</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 5392</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>649; 6201</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1871; 10289</t>
+          <t>0; 2609</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2694; 10956</t>
+          <t>2720; 10895</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2640; 10444</t>
+          <t>2408; 11070</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>646; 6616</t>
+          <t>650; 7094</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2388; 11075</t>
+          <t>2318; 10902</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>15919</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8349</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6299</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9262</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>19275</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>9636</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>9356</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>31282</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15919</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8349</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6299</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41023</t>
+          <t>16506</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13613; 28203</t>
+          <t>9852; 23333</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5181; 16126</t>
+          <t>4738; 14816</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5434; 15144</t>
+          <t>3160; 12253</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3409; 121848</t>
+          <t>4997; 15865</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10573; 23863</t>
+          <t>13041; 27491</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4595; 14072</t>
+          <t>5602; 15733</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3152; 11816</t>
+          <t>5349; 14758</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5599; 16017</t>
+          <t>3125; 18741</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26612; 44725</t>
+          <t>26158; 44427</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12034; 26919</t>
+          <t>12306; 25324</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9970; 22026</t>
+          <t>9986; 22931</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12891; 157028</t>
+          <t>10160; 28415</t>
         </is>
       </c>
     </row>
